--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/4420-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/4420-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23862D63-4E0C-478E-9F1F-89FBE5523A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5E14145-2B4A-4D88-A628-879025A2DC73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{5295B9E6-4BA8-4639-81AD-E88AC18E3F68}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{2E006DBF-5DB3-4AFD-AD0B-A3F9420DB898}"/>
   </bookViews>
   <sheets>
     <sheet name="4420-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1472,25 +1472,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7949AFB9-6AFF-41BD-ABC3-2D167D269543}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF962ED6-BDF5-433B-AC60-5EEB6DEF38B1}">
   <dimension ref="A1:R40"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1518,7 +1518,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1548,7 +1548,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1644,7 +1644,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>8.09</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>8.09</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>28.3</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="39">
         <v>2022</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>5.87</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="37">
         <v>2021</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>25</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>2020</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>8.16</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>25</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="37">
         <v>2019</v>
       </c>
@@ -2414,7 +2414,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>25</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>4.51</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="39">
         <v>2018</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>4.7699999999999996</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="37">
         <v>2017</v>
       </c>
@@ -2634,7 +2634,7 @@
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>2016</v>
       </c>
@@ -2688,7 +2688,7 @@
         <v>4.4400000000000004</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="37">
         <v>2015</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="39">
         <v>2014</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>3.69</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="37">
         <v>2013</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>5.15</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="39">
         <v>2012</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>6.54</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="37">
         <v>2011</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>6.18</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="39">
         <v>2010</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>5.54</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="37">
         <v>2009</v>
       </c>
@@ -3066,7 +3066,7 @@
         <v>6.31</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="39">
         <v>2008</v>
       </c>
@@ -3120,7 +3120,7 @@
         <v>7.08</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="37">
         <v>2007</v>
       </c>
@@ -3174,7 +3174,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="39">
         <v>2006</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>8.2899999999999991</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="37">
         <v>2005</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>9.26</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="39">
         <v>2004</v>
       </c>
@@ -3336,7 +3336,7 @@
         <v>8.3800000000000008</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="37">
         <v>2003</v>
       </c>
@@ -3390,7 +3390,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="39">
         <v>2002</v>
       </c>
@@ -3444,7 +3444,7 @@
         <v>6.27</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="37">
         <v>2001</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="39">
         <v>2000</v>
       </c>
@@ -3552,7 +3552,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="37" t="s">
         <v>43</v>
       </c>
